--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484256_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484256_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7212</v>
+        <v>5.647</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0359</v>
+        <v>5.6976</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6853</v>
+        <v>-0.0505</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3616</v>
+        <v>5.0139</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8363</v>
+        <v>2.8568</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5253</v>
+        <v>2.1571</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3166</v>
+        <v>5.8669</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1952</v>
+        <v>5.0576</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1214</v>
+        <v>0.8093</v>
       </c>
       <c r="M2" t="n">
-        <v>0.045</v>
+        <v>-0.853</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3589</v>
+        <v>-2.2008</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4039</v>
+        <v>1.3478</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1763</v>
+        <v>0.1726</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2122</v>
+        <v>0.6556</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0359</v>
+        <v>-0.483</v>
       </c>
       <c r="V2" t="n">
-        <v>2.16</v>
+        <v>1.8279</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4373</v>
+        <v>2.1052</v>
       </c>
       <c r="X2" t="n">
         <v>-0.2772</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0477</v>
+        <v>5.2045</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7987</v>
+        <v>3.5192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.249</v>
+        <v>1.6853</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0139</v>
+        <v>3.3616</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8568</v>
+        <v>2.8363</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1571</v>
+        <v>0.5253</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8669</v>
+        <v>3.3166</v>
       </c>
       <c r="K3" t="n">
-        <v>5.0576</v>
+        <v>3.1952</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8093</v>
+        <v>0.1214</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.853</v>
+        <v>0.045</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2008</v>
+        <v>-0.3589</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3478</v>
+        <v>0.4039</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5733</v>
+        <v>0.6596</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7567</v>
+        <v>0.6955</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1835</v>
+        <v>-0.0359</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8279</v>
+        <v>2.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1052</v>
+        <v>2.4373</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2772</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.587</v>
+        <v>4.9837</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4383</v>
+        <v>2.9439</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1487</v>
+        <v>2.0398</v>
       </c>
       <c r="G4" t="n">
         <v>-0.136</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.597</v>
+        <v>-1.2003</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.4023</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6891</v>
+        <v>-0.7981</v>
       </c>
       <c r="V4" t="n">
         <v>5.5387</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7641</v>
+        <v>1.9391</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6742</v>
+        <v>4.2057</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08989999999999999</v>
+        <v>-2.2666</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2304</v>
+        <v>1.472</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0821</v>
+        <v>-0.3492</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1482</v>
+        <v>1.8212</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3376</v>
+        <v>3.9286</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3236</v>
+        <v>1.4326</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6613</v>
+        <v>2.496</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.568</v>
+        <v>-2.4567</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7585</v>
+        <v>-1.7818</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8095</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.0998</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0594</v>
+        <v>0.0352</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1002</v>
+        <v>0.0646</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4063</v>
+        <v>1.4219</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7002</v>
+        <v>1.1686</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2938</v>
+        <v>0.2533</v>
       </c>
       <c r="G6" t="n">
-        <v>1.472</v>
+        <v>-1.2304</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3492</v>
+        <v>-1.0821</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8212</v>
+        <v>-0.1482</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9286</v>
+        <v>0.3376</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4326</v>
+        <v>-0.3236</v>
       </c>
       <c r="L6" t="n">
-        <v>2.496</v>
+        <v>0.6613</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4567</v>
+        <v>-1.568</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7818</v>
+        <v>-0.7585</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.8095</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4331</v>
+        <v>0.617</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4704</v>
+        <v>0.5538</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0374</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1155</v>
+        <v>0.6625</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6545</v>
+        <v>-0.1489</v>
       </c>
       <c r="F7" t="n">
-        <v>0.539</v>
+        <v>0.8114</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1031</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9342</v>
+        <v>-1.1563</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6657</v>
+        <v>-0.1602</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2685</v>
+        <v>-0.9961</v>
       </c>
       <c r="V7" t="n">
         <v>0.5545</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8581</v>
+        <v>-0.7025</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8337</v>
+        <v>-0.7325</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0245</v>
+        <v>0.03</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3065</v>
@@ -1078,13 +1078,13 @@
         <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8056</v>
+        <v>-0.65</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6052</v>
+        <v>-0.5041</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2004</v>
+        <v>-0.1459</v>
       </c>
       <c r="V8" t="n">
         <v>0.2772</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0808</v>
+        <v>-1.1819</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1241</v>
+        <v>0.023</v>
       </c>
       <c r="F9" t="n">
         <v>-1.2049</v>
@@ -1156,10 +1156,10 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5393</v>
+        <v>0.4382</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4458</v>
+        <v>0.3447</v>
       </c>
       <c r="U9" t="n">
         <v>0.0935</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2433</v>
+        <v>-2.7728</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9107</v>
+        <v>-2.304</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3326</v>
+        <v>-0.4687</v>
       </c>
       <c r="G10" t="n">
         <v>-0.126</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5546</v>
+        <v>-1.0841</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.2406</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7073</v>
+        <v>-0.8435</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2592</v>
+        <v>-5.2319</v>
       </c>
       <c r="E11" t="n">
         <v>-3.8028</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4564</v>
+        <v>-1.4291</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7889</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6889</v>
+        <v>-0.6617</v>
       </c>
       <c r="T11" t="n">
         <v>0.08260000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7716</v>
+        <v>-0.7443</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.969399999999998</v>
+        <v>9.9696</v>
       </c>
       <c r="E12" t="n">
-        <v>10.5697</v>
+        <v>10.5698</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6002999999999996</v>
+        <v>-0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.950499999999998</v>
+        <v>2.950499999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.837000000000002</v>
+        <v>-7.837000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>10.7878</v>
@@ -1366,7 +1366,7 @@
         <v>14.0564</v>
       </c>
       <c r="K12" t="n">
-        <v>7.308700000000002</v>
+        <v>7.3087</v>
       </c>
       <c r="L12" t="n">
         <v>6.7478</v>
@@ -1378,7 +1378,7 @@
         <v>-15.1457</v>
       </c>
       <c r="O12" t="n">
-        <v>4.039699999999999</v>
+        <v>4.0397</v>
       </c>
       <c r="P12" t="n">
         <v>0.9768</v>
@@ -1390,13 +1390,13 @@
         <v>16.6041</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.765299999999999</v>
+        <v>-2.7652</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0603</v>
+        <v>1.0602</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.8256</v>
+        <v>-3.8255</v>
       </c>
       <c r="V12" t="n">
         <v>8.807600000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5165</v>
+        <v>3.9906</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1045</v>
+        <v>4.0786</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.588</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0823</v>
+        <v>1.4829</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5634</v>
+        <v>0.8222</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.481</v>
+        <v>0.6607</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2046</v>
+        <v>3.0558</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6061</v>
+        <v>1.7204</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4015</v>
+        <v>1.3354</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1223</v>
+        <v>-1.5729</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0427</v>
+        <v>-0.8982</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0795</v>
+        <v>-0.6747</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7813</v>
+        <v>0.531</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6813</v>
+        <v>0.1363</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1</v>
+        <v>0.3948</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2905</v>
+        <v>3.3837</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7451</v>
+        <v>2.9474</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5453</v>
+        <v>0.4364</v>
       </c>
       <c r="G14" t="n">
         <v>4.7303</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1695</v>
+        <v>0.2628</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1432</v>
+        <v>0.3454</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0263</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2186</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2478</v>
+        <v>2.5428</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4719</v>
+        <v>5.2956</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2241</v>
+        <v>-2.7528</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4829</v>
+        <v>1.0823</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8222</v>
+        <v>3.5634</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6607</v>
+        <v>-2.481</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0558</v>
+        <v>3.2046</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7204</v>
+        <v>4.6061</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3354</v>
+        <v>-1.4015</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5729</v>
+        <v>-2.1223</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8982</v>
+        <v>-1.0427</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6747</v>
+        <v>-1.0795</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2118</v>
+        <v>0.8076</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4704</v>
+        <v>0.8724</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2586</v>
+        <v>-0.0648</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6093</v>
+        <v>-1.4959</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4155</v>
+        <v>2.0596</v>
       </c>
       <c r="E16" t="n">
-        <v>3.05</v>
+        <v>3.8589</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6346</v>
+        <v>-1.7993</v>
       </c>
       <c r="G16" t="n">
         <v>1.6782</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9427</v>
+        <v>-0.2985</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.773</v>
+        <v>0.0359</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1697</v>
+        <v>-0.3344</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2735</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9776</v>
+        <v>1.1993</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2796</v>
+        <v>0.0237</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2572</v>
+        <v>1.1755</v>
       </c>
       <c r="G17" t="n">
         <v>0.2178</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0215</v>
+        <v>0.2001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3026</v>
+        <v>0.0007</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2811</v>
+        <v>0.1994</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3847</v>
+        <v>-0.032</v>
       </c>
       <c r="E18" t="n">
         <v>1.7199</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1047</v>
+        <v>-1.752</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4099</v>
@@ -1858,13 +1858,13 @@
         <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0417</v>
+        <v>0.311</v>
       </c>
       <c r="T18" t="n">
         <v>0.6219</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6637</v>
+        <v>-0.311</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4959</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3138</v>
+        <v>-1.2514</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4957</v>
+        <v>-1.6628</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8181</v>
+        <v>0.4114</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.4759</v>
+        <v>0.517</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2507</v>
+        <v>0.6657</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2252</v>
+        <v>-0.1486</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4286</v>
+        <v>1.2061</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2827</v>
+        <v>1.0847</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1459</v>
+        <v>0.1214</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0474</v>
+        <v>-0.6891</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.968</v>
+        <v>-0.419</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0793</v>
+        <v>-0.27</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3808</v>
+        <v>0.185</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9096</v>
+        <v>0.0613</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5288</v>
+        <v>0.1238</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6092</v>
+        <v>-1.9723</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9661</v>
+        <v>-1.5068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3569</v>
+        <v>-0.4654</v>
       </c>
       <c r="G20" t="n">
-        <v>0.517</v>
+        <v>-3.4759</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6657</v>
+        <v>-1.2507</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1486</v>
+        <v>-2.2252</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2061</v>
+        <v>-1.4286</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0847</v>
+        <v>-0.2827</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>-1.1459</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6891</v>
+        <v>-2.0474</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.419</v>
+        <v>-0.968</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.27</v>
+        <v>-1.0793</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1728</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2421</v>
+        <v>0.8985</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0693</v>
+        <v>-0.1761</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0499</v>
+        <v>-5.7115</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1236</v>
+        <v>-2.9214</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9263</v>
+        <v>-2.7902</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3888</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.4595</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4842</v>
+        <v>-0.282</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3137</v>
+        <v>-0.1775</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4959</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2011</v>
+        <v>-6.5487</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5163</v>
+        <v>-5.9077</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6848</v>
+        <v>-0.641</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2692</v>
+        <v>-3.1151</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4659</v>
+        <v>-2.6291</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.7351</v>
+        <v>-0.486</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1008</v>
+        <v>-1.4768</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2292</v>
+        <v>-2.2052</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.33</v>
+        <v>0.7284</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1684</v>
+        <v>-1.6382</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7634</v>
+        <v>-0.4239</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4051</v>
+        <v>-1.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>-4.8836</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4588</v>
+        <v>0.4732</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4914</v>
+        <v>0.4527</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0326</v>
+        <v>0.0206</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8585</v>
+        <v>-6.9556</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.11</v>
+        <v>-5.3252</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7486</v>
+        <v>-1.6303</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1151</v>
+        <v>-3.2692</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6291</v>
+        <v>0.4659</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.486</v>
+        <v>-3.7351</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4768</v>
+        <v>-2.1008</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2052</v>
+        <v>1.2292</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7284</v>
+        <v>-3.33</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6382</v>
+        <v>-1.1684</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4239</v>
+        <v>-0.7634</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2144</v>
+        <v>-0.4051</v>
       </c>
       <c r="P23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-3.9069</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-4.8836</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1634</v>
+        <v>0.7044</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2504</v>
+        <v>0.6824</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.0219</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.9693</v>
+        <v>-9.295499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6000999999999994</v>
+        <v>0.6002000000000018</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.5698</v>
+        <v>-9.8956</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.950399999999999</v>
+        <v>-2.950400000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8372</v>
+        <v>7.837199999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-10.7875</v>
@@ -2305,7 +2305,7 @@
         <v>15.1459</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.039600000000001</v>
+        <v>-4.0396</v>
       </c>
       <c r="M24" t="n">
         <v>-14.0566</v>
@@ -2317,7 +2317,7 @@
         <v>-6.7479</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9767000000000006</v>
+        <v>-0.9767000000000003</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.6041</v>
@@ -2326,13 +2326,13 @@
         <v>15.6273</v>
       </c>
       <c r="S24" t="n">
-        <v>2.765400000000001</v>
+        <v>3.4394</v>
       </c>
       <c r="T24" t="n">
         <v>3.8255</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0602</v>
+        <v>-0.3859</v>
       </c>
       <c r="V24" t="n">
         <v>-8.8078</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484256_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484256_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1094,6 +1129,11 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,542 +1462,573 @@
       <c r="X12" t="n">
         <v>-2.2726</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9906</v>
+        <v>3.3837</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0786</v>
+        <v>2.9474</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.4364</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4829</v>
+        <v>4.7303</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8222</v>
+        <v>4.8251</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6607</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0558</v>
+        <v>5.2196</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7204</v>
+        <v>5.1791</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3354</v>
+        <v>0.0405</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5729</v>
+        <v>-0.4893</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8982</v>
+        <v>-0.354</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6747</v>
+        <v>-0.1352</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.531</v>
+        <v>0.2628</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1363</v>
+        <v>0.3454</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3948</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8865</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3837</v>
+        <v>2.7489</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9474</v>
+        <v>2.7489</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4364</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7303</v>
+        <v>2.7489</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8251</v>
+        <v>1.5349</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09470000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2196</v>
+        <v>2.7489</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1791</v>
+        <v>1.5349</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>1.214</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4893</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1352</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2628</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3454</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5428</v>
+        <v>2.4697</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2956</v>
+        <v>2.5576</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7528</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0823</v>
+        <v>-0.0381</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5634</v>
+        <v>0.5152</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.481</v>
+        <v>-0.5533</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2046</v>
+        <v>1.5348</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6061</v>
+        <v>1.4134</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4015</v>
+        <v>0.1214</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1223</v>
+        <v>-1.5729</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0427</v>
+        <v>-0.8982</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0795</v>
+        <v>-0.6747</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8076</v>
+        <v>0.531</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8724</v>
+        <v>0.1363</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0648</v>
+        <v>0.3948</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0596</v>
+        <v>1.521</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8589</v>
+        <v>1.521</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7993</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6782</v>
+        <v>1.521</v>
       </c>
       <c r="H16" t="n">
-        <v>3.526</v>
+        <v>0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8478</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9913</v>
+        <v>1.521</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2991</v>
+        <v>0.307</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3077</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3131</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7731</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5401</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2985</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0359</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3344</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2735</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1993</v>
+        <v>1.4456</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0237</v>
+        <v>3.245</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1755</v>
+        <v>-1.7993</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2178</v>
+        <v>1.0642</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08309999999999999</v>
+        <v>2.912</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1346</v>
+        <v>-1.8478</v>
       </c>
       <c r="J17" t="n">
-        <v>0.023</v>
+        <v>2.3774</v>
       </c>
       <c r="K17" t="n">
-        <v>0.023</v>
+        <v>3.6851</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.3077</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1948</v>
+        <v>-1.3131</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0601</v>
+        <v>-0.7731</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1346</v>
+        <v>-0.5401</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2001</v>
+        <v>-0.2985</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0007</v>
+        <v>0.0359</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1994</v>
+        <v>-0.3344</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2735</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.032</v>
+        <v>1.1993</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7199</v>
+        <v>0.0237</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.752</v>
+        <v>1.1755</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4099</v>
+        <v>0.2178</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7488</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3389</v>
+        <v>0.1346</v>
       </c>
       <c r="J18" t="n">
-        <v>1.098</v>
+        <v>0.023</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0844</v>
+        <v>0.023</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0136</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5079</v>
+        <v>0.1948</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.0601</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6747</v>
+        <v>0.1346</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.311</v>
+        <v>0.2001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6219</v>
+        <v>0.0007</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.311</v>
+        <v>0.1994</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2514</v>
+        <v>0.614</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6628</v>
+        <v>0.614</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4114</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.517</v>
+        <v>0.614</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6657</v>
+        <v>0.614</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1486</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2061</v>
+        <v>0.614</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0847</v>
+        <v>0.614</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6891</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.419</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0613</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,231 +2038,246 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9723</v>
+        <v>-0.032</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5068</v>
+        <v>1.7199</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4654</v>
+        <v>-1.752</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4759</v>
+        <v>-0.4099</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2507</v>
+        <v>-0.7488</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2252</v>
+        <v>0.3389</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4286</v>
+        <v>1.098</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2827</v>
+        <v>0.0844</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1459</v>
+        <v>1.0136</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0474</v>
+        <v>-1.5079</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.968</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0793</v>
+        <v>-0.6747</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8985</v>
+        <v>0.6219</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1761</v>
+        <v>-0.311</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7115</v>
+        <v>-0.2061</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9214</v>
+        <v>2.5467</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7902</v>
+        <v>-2.7528</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3888</v>
+        <v>-1.6666</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4856</v>
+        <v>2.0284</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9033</v>
+        <v>-3.695</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6860000000000001</v>
+        <v>0.4557</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5921999999999999</v>
+        <v>3.0711</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-2.6155</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7028</v>
+        <v>-2.1223</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8933</v>
+        <v>-1.0427</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8095</v>
+        <v>-1.0795</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4595</v>
+        <v>0.8076</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.282</v>
+        <v>0.8724</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1775</v>
+        <v>-0.0648</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5487</v>
+        <v>-1.2514</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9077</v>
+        <v>-1.6628</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.641</v>
+        <v>0.4114</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1151</v>
+        <v>0.517</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6291</v>
+        <v>0.6657</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.486</v>
+        <v>-0.1486</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4768</v>
+        <v>1.2061</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2052</v>
+        <v>1.0847</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7284</v>
+        <v>0.1214</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6382</v>
+        <v>-0.6891</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4239</v>
+        <v>-0.419</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2144</v>
+        <v>-0.27</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.8836</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4732</v>
+        <v>0.185</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4527</v>
+        <v>0.0613</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0206</v>
+        <v>0.1238</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,163 +2287,423 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9556</v>
+        <v>-1.9723</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3252</v>
+        <v>-1.5068</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6303</v>
+        <v>-0.4654</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2692</v>
+        <v>-3.4759</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4659</v>
+        <v>-1.2507</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7351</v>
+        <v>-2.2252</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1008</v>
+        <v>-1.4286</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2292</v>
+        <v>-0.2827</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.33</v>
+        <v>-1.1459</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1684</v>
+        <v>-2.0474</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7634</v>
+        <v>-0.968</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4051</v>
+        <v>-1.0793</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7044</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6824</v>
+        <v>0.8985</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0219</v>
+        <v>-0.1761</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.295499999999999</v>
+        <v>-5.7115</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6002000000000018</v>
+        <v>-2.9214</v>
       </c>
       <c r="F24" t="n">
+        <v>-2.7902</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.3888</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.4856</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.9033</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.6860000000000001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.5921999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.09379999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.7028</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.8933</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.8095</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.4595</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.282</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1775</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. HERETER MARCHANTE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.5487</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.9077</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.641</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.1151</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.6291</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.486</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.4768</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.2052</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.7284</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.6382</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.4239</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.2144</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. JAIME BATLLE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-6.9556</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.3252</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.6303</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.2692</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4659</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-3.7351</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.1008</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.2292</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.1684</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7634</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484256_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-9.295399999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6002999999999981</v>
+      </c>
+      <c r="F27" t="n">
         <v>-9.8956</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>-2.950400000000001</v>
       </c>
-      <c r="H24" t="n">
-        <v>7.837199999999999</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H27" t="n">
+        <v>7.8371</v>
+      </c>
+      <c r="I27" t="n">
         <v>-10.7875</v>
       </c>
-      <c r="J24" t="n">
-        <v>11.1062</v>
-      </c>
-      <c r="K24" t="n">
-        <v>15.1459</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="J27" t="n">
+        <v>11.1063</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15.1458</v>
+      </c>
+      <c r="L27" t="n">
         <v>-4.0396</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>-14.0566</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>-7.308699999999999</v>
       </c>
-      <c r="O24" t="n">
-        <v>-6.7479</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="O27" t="n">
+        <v>-6.747899999999999</v>
+      </c>
+      <c r="P27" t="n">
         <v>-0.9767000000000003</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-16.6041</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>15.6273</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>3.4394</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>3.8255</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>-0.3859</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>-8.8078</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>2.2726</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-11.0805</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
